--- a/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CALVA</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>LORENA</t>
   </si>
 </sst>
 </file>
@@ -655,16 +646,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>96.43000000000001</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -678,16 +672,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -701,16 +698,19 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>92</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -724,16 +724,19 @@
         <v>21</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>21</v>
       </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -747,16 +750,19 @@
         <v>10</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -812,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -838,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -864,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G4">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -890,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>85.70999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -925,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -965,29 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>23330051920215</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>JHON STEVE</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920238</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="26">
   <si>
     <t>Mat</t>
   </si>
@@ -79,13 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>JHON STEVE</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
+  </si>
+  <si>
+    <t>VANESA</t>
   </si>
 </sst>
 </file>
@@ -862,7 +871,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,16 +888,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,16 +914,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>90.48</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -940,7 +949,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -982,25 +991,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920238</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>23330051920237</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
